--- a/Financials.xlsx
+++ b/Financials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="13" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t>Balance Sheet</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>Saturday,December 23,2023</t>
+  </si>
+  <si>
+    <t>neo admission</t>
   </si>
 </sst>
 </file>
@@ -820,7 +823,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1421,12 +1424,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:E25"/>
+  <dimension ref="B2:E27"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
     <col min="2" max="3" width="12.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" style="4" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
@@ -1477,22 +1480,40 @@
       </c>
     </row>
     <row r="7" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B7" s="28"/>
+      <c r="B7" s="29">
+        <v>45301</v>
+      </c>
       <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="28"/>
+      <c r="D7" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="28">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="22.5" customHeight="1">
+      <c r="B8" s="29">
+        <v>45327</v>
+      </c>
       <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
+      <c r="D8" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="28">
+        <v>10000</v>
+      </c>
     </row>
     <row r="9" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B9" s="28"/>
+      <c r="B9" s="29">
+        <v>45380</v>
+      </c>
       <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
+      <c r="D9" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="28">
+        <v>500</v>
+      </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="28"/>
@@ -1506,7 +1527,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
     </row>
-    <row r="12" spans="2:5" ht="22.5" customHeight="1">
+    <row r="12" spans="2:5">
       <c r="B12" s="28"/>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
@@ -1536,15 +1557,27 @@
       <c r="D16" s="28"/>
       <c r="E16" s="28"/>
     </row>
-    <row r="17" ht="22.5" customHeight="1"/>
-    <row r="18" ht="22.5" customHeight="1"/>
-    <row r="19" ht="22.5" customHeight="1"/>
-    <row r="20" ht="22.5" customHeight="1"/>
-    <row r="21" ht="22.5" customHeight="1"/>
-    <row r="22" ht="22.5" customHeight="1"/>
-    <row r="23" ht="22.5" customHeight="1"/>
-    <row r="24" ht="22.5" customHeight="1"/>
-    <row r="25" ht="22.5" customHeight="1"/>
+    <row r="17" spans="2:5" ht="22.5" customHeight="1">
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+    </row>
+    <row r="18" spans="2:5" ht="22.5" customHeight="1">
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+    </row>
+    <row r="19" spans="2:5" ht="22.5" customHeight="1"/>
+    <row r="20" spans="2:5" ht="22.5" customHeight="1"/>
+    <row r="21" spans="2:5" ht="22.5" customHeight="1"/>
+    <row r="22" spans="2:5" ht="22.5" customHeight="1"/>
+    <row r="23" spans="2:5" ht="22.5" customHeight="1"/>
+    <row r="24" spans="2:5" ht="22.5" customHeight="1"/>
+    <row r="25" spans="2:5" ht="22.5" customHeight="1"/>
+    <row r="26" spans="2:5" ht="22.5" customHeight="1"/>
+    <row r="27" spans="2:5" ht="22.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Financials.xlsx
+++ b/Financials.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="13" r:id="rId1"/>
     <sheet name="BalanceSheet" sheetId="12" r:id="rId2"/>
     <sheet name="Expenses" sheetId="14" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
+  <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -251,13 +251,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -823,16 +823,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F31"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="32.7109375" style="4" customWidth="1"/>
@@ -843,7 +843,7 @@
     <col min="7" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="22.5" customHeight="1">
+    <row r="2" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>39</v>
       </c>
@@ -853,7 +853,7 @@
         <v>45219</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="22.5" customHeight="1">
+    <row r="4" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>31</v>
       </c>
@@ -865,7 +865,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="22.5" customHeight="1">
+    <row r="5" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>29</v>
       </c>
@@ -875,10 +875,10 @@
       <c r="D5" s="35"/>
       <c r="E5" s="6">
         <f>SUM(E13:E24)</f>
-        <v>156000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="22.5" customHeight="1">
+        <v>161000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18" t="s">
         <v>30</v>
       </c>
@@ -892,7 +892,7 @@
       </c>
       <c r="F6" s="31"/>
     </row>
-    <row r="7" spans="2:6" ht="22.5" customHeight="1">
+    <row r="7" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>48</v>
       </c>
@@ -900,23 +900,23 @@
       <c r="D7" s="35"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
-    <row r="9" spans="2:6" ht="22.5" customHeight="1">
+    <row r="9" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="21" t="s">
         <v>34</v>
       </c>
       <c r="E9" s="22">
         <f>SUM(E12:E30)</f>
-        <v>173380</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="15">
+        <v>178380</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="15" x14ac:dyDescent="0.25">
       <c r="E10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="22.5" customHeight="1">
+    <row r="11" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="21" t="s">
         <v>35</v>
       </c>
@@ -924,7 +924,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="22.5" customHeight="1">
+    <row r="12" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="9" t="s">
         <v>29</v>
       </c>
@@ -932,7 +932,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="22.5" customHeight="1">
+    <row r="13" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="20">
         <v>45180</v>
       </c>
@@ -941,7 +941,7 @@
       </c>
       <c r="F13" s="30"/>
     </row>
-    <row r="14" spans="2:6" ht="22.5" customHeight="1">
+    <row r="14" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="9">
         <v>45256</v>
       </c>
@@ -951,7 +951,7 @@
       </c>
       <c r="F14" s="30"/>
     </row>
-    <row r="15" spans="2:6" ht="22.5" customHeight="1">
+    <row r="15" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="20">
         <v>45272</v>
       </c>
@@ -960,7 +960,7 @@
       </c>
       <c r="F15" s="31"/>
     </row>
-    <row r="16" spans="2:6" ht="22.5" customHeight="1">
+    <row r="16" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="9">
         <v>45274</v>
       </c>
@@ -968,7 +968,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="17" spans="4:5" ht="22.5" customHeight="1">
+    <row r="17" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="20">
         <v>45275</v>
       </c>
@@ -976,7 +976,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="18" spans="4:5" ht="22.5" customHeight="1">
+    <row r="18" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="20">
         <v>45278</v>
       </c>
@@ -984,7 +984,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="19" spans="4:5" ht="22.5" customHeight="1">
+    <row r="19" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="9" t="s">
         <v>55</v>
       </c>
@@ -992,7 +992,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="20" spans="4:5" ht="22.5" customHeight="1">
+    <row r="20" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="9">
         <v>45322</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="21" spans="4:5" ht="22.5" customHeight="1">
+    <row r="21" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="9">
         <v>45336</v>
       </c>
@@ -1008,25 +1008,29 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="22" spans="4:5" ht="22.5" customHeight="1">
-      <c r="D22" s="9"/>
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="4:5" ht="22.5" customHeight="1">
+    <row r="22" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="9">
+        <v>45368</v>
+      </c>
+      <c r="E22" s="6">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="23" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="26"/>
       <c r="E23" s="27"/>
     </row>
-    <row r="24" spans="4:5" ht="22.5" customHeight="1">
+    <row r="24" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="9"/>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" spans="4:5" ht="22.5" customHeight="1">
+    <row r="25" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="9" t="s">
         <v>30</v>
       </c>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" spans="4:5" ht="22.5" customHeight="1">
+    <row r="26" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="20">
         <v>45180</v>
       </c>
@@ -1034,23 +1038,23 @@
         <v>17380</v>
       </c>
     </row>
-    <row r="27" spans="4:5" ht="22.5" customHeight="1">
+    <row r="27" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="9"/>
       <c r="E27" s="6"/>
     </row>
-    <row r="28" spans="4:5" ht="22.5" customHeight="1">
+    <row r="28" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="20"/>
       <c r="E28" s="19"/>
     </row>
-    <row r="29" spans="4:5" ht="22.5" customHeight="1">
+    <row r="29" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="9"/>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" spans="4:5" ht="22.5" customHeight="1">
+    <row r="30" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="20"/>
       <c r="E30" s="19"/>
     </row>
-    <row r="31" spans="4:5" ht="15">
+    <row r="31" spans="4:5" ht="15" x14ac:dyDescent="0.25">
       <c r="D31" s="10"/>
     </row>
   </sheetData>
@@ -1066,9 +1070,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E44"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="12"/>
     <col min="2" max="2" width="13.28515625" style="12" customWidth="1"/>
@@ -1078,10 +1082,10 @@
     <col min="6" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15">
+    <row r="1" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B1" s="11"/>
     </row>
-    <row r="2" spans="2:5" ht="22.5" customHeight="1">
+    <row r="2" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="23" t="s">
         <v>0</v>
       </c>
@@ -1089,7 +1093,7 @@
       <c r="D2" s="24"/>
       <c r="E2" s="25"/>
     </row>
-    <row r="3" spans="2:5" ht="22.5" customHeight="1">
+    <row r="3" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="13" t="s">
         <v>39</v>
       </c>
@@ -1099,7 +1103,7 @@
         <v>45219</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="22.5" customHeight="1">
+    <row r="4" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="15" t="s">
         <v>1</v>
       </c>
@@ -1107,7 +1111,7 @@
       <c r="D4" s="14"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="2:5" ht="22.5" customHeight="1">
+    <row r="5" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="13"/>
       <c r="C5" s="17" t="s">
         <v>2</v>
@@ -1115,7 +1119,7 @@
       <c r="D5" s="14"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="2:5" ht="22.5" customHeight="1">
+    <row r="6" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
       <c r="C6" s="14"/>
       <c r="D6" s="16" t="s">
@@ -1123,7 +1127,7 @@
       </c>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" spans="2:5" ht="22.5" customHeight="1">
+    <row r="7" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1"/>
       <c r="C7" s="14"/>
       <c r="D7" s="16" t="s">
@@ -1131,7 +1135,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="2:5" ht="22.5" customHeight="1">
+    <row r="8" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
       <c r="C8" s="14"/>
       <c r="D8" s="16" t="s">
@@ -1139,7 +1143,7 @@
       </c>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="2:5" ht="22.5" customHeight="1">
+    <row r="9" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="14"/>
       <c r="D9" s="17" t="s">
@@ -1147,7 +1151,7 @@
       </c>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="2:5" ht="22.5" customHeight="1">
+    <row r="10" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="13"/>
       <c r="C10" s="17" t="s">
         <v>3</v>
@@ -1155,7 +1159,7 @@
       <c r="D10" s="14"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="2:5" ht="22.5" customHeight="1">
+    <row r="11" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
       <c r="D11" s="16" t="s">
@@ -1163,7 +1167,7 @@
       </c>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="2:5" ht="22.5" customHeight="1">
+    <row r="12" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="13"/>
       <c r="C12" s="14"/>
       <c r="D12" s="16" t="s">
@@ -1171,7 +1175,7 @@
       </c>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="2:5" ht="22.5" customHeight="1">
+    <row r="13" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="13"/>
       <c r="C13" s="14"/>
       <c r="D13" s="16" t="s">
@@ -1179,7 +1183,7 @@
       </c>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="2:5" ht="22.5" customHeight="1">
+    <row r="14" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="13"/>
       <c r="C14" s="14"/>
       <c r="D14" s="16" t="s">
@@ -1187,7 +1191,7 @@
       </c>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="2:5" ht="22.5" customHeight="1">
+    <row r="15" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="13"/>
       <c r="C15" s="14"/>
       <c r="D15" s="17" t="s">
@@ -1195,13 +1199,13 @@
       </c>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="2:5" ht="22.5" customHeight="1">
+    <row r="16" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="13"/>
       <c r="C16" s="16"/>
       <c r="D16" s="14"/>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" spans="2:5" ht="22.5" customHeight="1">
+    <row r="17" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="13"/>
       <c r="C17" s="17" t="s">
         <v>4</v>
@@ -1209,7 +1213,7 @@
       <c r="D17" s="14"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="2:5" ht="22.5" customHeight="1">
+    <row r="18" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="13"/>
       <c r="C18" s="16"/>
       <c r="D18" s="16" t="s">
@@ -1217,7 +1221,7 @@
       </c>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" spans="2:5" ht="22.5" customHeight="1">
+    <row r="19" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="13"/>
       <c r="C19" s="16"/>
       <c r="D19" s="16" t="s">
@@ -1225,7 +1229,7 @@
       </c>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="2:5" ht="22.5" customHeight="1">
+    <row r="20" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="13"/>
       <c r="C20" s="16"/>
       <c r="D20" s="16" t="s">
@@ -1233,7 +1237,7 @@
       </c>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="2:5" ht="22.5" customHeight="1">
+    <row r="21" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="13"/>
       <c r="C21" s="16"/>
       <c r="D21" s="16" t="s">
@@ -1241,7 +1245,7 @@
       </c>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="2:5" ht="22.5" customHeight="1">
+    <row r="22" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="13"/>
       <c r="C22" s="16"/>
       <c r="D22" s="17" t="s">
@@ -1249,13 +1253,13 @@
       </c>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="2:5" ht="22.5" customHeight="1">
+    <row r="23" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="13"/>
       <c r="C23" s="16"/>
       <c r="D23" s="14"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="2:5" ht="22.5" customHeight="1">
+    <row r="24" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="15" t="s">
         <v>5</v>
       </c>
@@ -1263,7 +1267,7 @@
       <c r="D24" s="14"/>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="2:5" ht="22.5" customHeight="1">
+    <row r="25" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="13"/>
       <c r="C25" s="17" t="s">
         <v>6</v>
@@ -1271,7 +1275,7 @@
       <c r="D25" s="14"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="2:5" ht="22.5" customHeight="1">
+    <row r="26" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="13"/>
       <c r="C26" s="16"/>
       <c r="D26" s="16" t="s">
@@ -1279,7 +1283,7 @@
       </c>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="2:5" ht="22.5" customHeight="1">
+    <row r="27" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="13"/>
       <c r="C27" s="16"/>
       <c r="D27" s="16" t="s">
@@ -1287,7 +1291,7 @@
       </c>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="2:5" ht="22.5" customHeight="1">
+    <row r="28" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="13"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
@@ -1295,7 +1299,7 @@
       </c>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="2:5" ht="22.5" customHeight="1">
+    <row r="29" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="13"/>
       <c r="C29" s="16"/>
       <c r="D29" s="16" t="s">
@@ -1303,7 +1307,7 @@
       </c>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" spans="2:5" ht="22.5" customHeight="1">
+    <row r="30" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="13"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17" t="s">
@@ -1311,13 +1315,13 @@
       </c>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="2:5" ht="22.5" customHeight="1">
+    <row r="31" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="13"/>
       <c r="C31" s="16"/>
       <c r="D31" s="14"/>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="2:5" ht="22.5" customHeight="1">
+    <row r="32" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="13"/>
       <c r="C32" s="17" t="s">
         <v>7</v>
@@ -1325,7 +1329,7 @@
       <c r="D32" s="14"/>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="2:5" ht="22.5" customHeight="1">
+    <row r="33" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="13"/>
       <c r="C33" s="16"/>
       <c r="D33" s="16" t="s">
@@ -1333,7 +1337,7 @@
       </c>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="2:5" ht="22.5" customHeight="1">
+    <row r="34" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="13"/>
       <c r="C34" s="16"/>
       <c r="D34" s="16" t="s">
@@ -1341,7 +1345,7 @@
       </c>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="2:5" ht="22.5" customHeight="1">
+    <row r="35" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="13"/>
       <c r="C35" s="16"/>
       <c r="D35" s="17" t="s">
@@ -1349,7 +1353,7 @@
       </c>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" spans="2:5" ht="22.5" customHeight="1">
+    <row r="36" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="13"/>
       <c r="C36" s="16"/>
       <c r="D36" s="15" t="s">
@@ -1357,13 +1361,13 @@
       </c>
       <c r="E36" s="3"/>
     </row>
-    <row r="37" spans="2:5" ht="22.5" customHeight="1">
+    <row r="37" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="13"/>
       <c r="C37" s="16"/>
       <c r="D37" s="14"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="2:5" ht="22.5" customHeight="1">
+    <row r="38" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1371,7 +1375,7 @@
       <c r="D38" s="14"/>
       <c r="E38" s="3"/>
     </row>
-    <row r="39" spans="2:5" ht="22.5" customHeight="1">
+    <row r="39" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="13"/>
       <c r="C39" s="16" t="s">
         <v>9</v>
@@ -1379,7 +1383,7 @@
       <c r="D39" s="14"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="2:5" ht="22.5" customHeight="1">
+    <row r="40" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="13"/>
       <c r="C40" s="16" t="s">
         <v>27</v>
@@ -1387,7 +1391,7 @@
       <c r="D40" s="14"/>
       <c r="E40" s="3"/>
     </row>
-    <row r="41" spans="2:5" ht="22.5" customHeight="1">
+    <row r="41" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="13"/>
       <c r="C41" s="16" t="s">
         <v>28</v>
@@ -1395,7 +1399,7 @@
       <c r="D41" s="14"/>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="2:5" ht="22.5" customHeight="1">
+    <row r="42" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="13"/>
       <c r="C42" s="16" t="s">
         <v>40</v>
@@ -1403,13 +1407,13 @@
       <c r="D42" s="14"/>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="2:5" ht="22.5" customHeight="1">
+    <row r="43" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="13"/>
       <c r="C43" s="16"/>
       <c r="D43" s="14"/>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="2:5" ht="22.5" customHeight="1">
+    <row r="44" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="13"/>
       <c r="C44" s="17" t="s">
         <v>47</v>
@@ -1423,9 +1427,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
     <col min="2" max="3" width="12.7109375" style="4" customWidth="1"/>
@@ -1433,13 +1437,13 @@
     <col min="5" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="22.5" customHeight="1"/>
-    <row r="3" spans="2:5">
+    <row r="2" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="22.5" customHeight="1">
+    <row r="4" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
         <v>35</v>
       </c>
@@ -1453,7 +1457,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="22.5" customHeight="1">
+    <row r="5" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="29">
         <v>45274</v>
       </c>
@@ -1467,7 +1471,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="22.5" customHeight="1">
+    <row r="6" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="29">
         <v>45283</v>
       </c>
@@ -1479,7 +1483,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="22.5" customHeight="1">
+    <row r="7" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="29">
         <v>45301</v>
       </c>
@@ -1491,7 +1495,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="22.5" customHeight="1">
+    <row r="8" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="29">
         <v>45327</v>
       </c>
@@ -1503,7 +1507,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="22.5" customHeight="1">
+    <row r="9" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="29">
         <v>45380</v>
       </c>
@@ -1515,69 +1519,69 @@
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
       <c r="E10" s="28"/>
     </row>
-    <row r="11" spans="2:5" ht="22.5" customHeight="1">
+    <row r="11" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="28"/>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
       <c r="E12" s="28"/>
     </row>
-    <row r="13" spans="2:5" ht="22.5" customHeight="1">
+    <row r="13" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
     </row>
-    <row r="14" spans="2:5" ht="22.5" customHeight="1">
+    <row r="14" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
       <c r="E14" s="28"/>
     </row>
-    <row r="15" spans="2:5" ht="22.5" customHeight="1">
+    <row r="15" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="28"/>
       <c r="C15" s="28"/>
       <c r="D15" s="28"/>
       <c r="E15" s="28"/>
     </row>
-    <row r="16" spans="2:5" ht="22.5" customHeight="1">
+    <row r="16" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
       <c r="E16" s="28"/>
     </row>
-    <row r="17" spans="2:5" ht="22.5" customHeight="1">
+    <row r="17" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>
       <c r="E17" s="28"/>
     </row>
-    <row r="18" spans="2:5" ht="22.5" customHeight="1">
+    <row r="18" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
       <c r="E18" s="28"/>
     </row>
-    <row r="19" spans="2:5" ht="22.5" customHeight="1"/>
-    <row r="20" spans="2:5" ht="22.5" customHeight="1"/>
-    <row r="21" spans="2:5" ht="22.5" customHeight="1"/>
-    <row r="22" spans="2:5" ht="22.5" customHeight="1"/>
-    <row r="23" spans="2:5" ht="22.5" customHeight="1"/>
-    <row r="24" spans="2:5" ht="22.5" customHeight="1"/>
-    <row r="25" spans="2:5" ht="22.5" customHeight="1"/>
-    <row r="26" spans="2:5" ht="22.5" customHeight="1"/>
-    <row r="27" spans="2:5" ht="22.5" customHeight="1"/>
+    <row r="19" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Financials.xlsx
+++ b/Financials.xlsx
@@ -823,7 +823,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -875,7 +875,7 @@
       <c r="D5" s="35"/>
       <c r="E5" s="6">
         <f>SUM(E13:E24)</f>
-        <v>161000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -910,7 +910,7 @@
       </c>
       <c r="E9" s="22">
         <f>SUM(E12:E30)</f>
-        <v>178380</v>
+        <v>188380</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="15" x14ac:dyDescent="0.25">
@@ -1017,8 +1017,12 @@
       </c>
     </row>
     <row r="23" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="26"/>
-      <c r="E23" s="27"/>
+      <c r="D23" s="26">
+        <v>45466</v>
+      </c>
+      <c r="E23" s="27">
+        <v>10000</v>
+      </c>
     </row>
     <row r="24" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="9"/>

--- a/Financials.xlsx
+++ b/Financials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="13" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
   <si>
     <t>Balance Sheet</t>
   </si>
@@ -247,15 +247,19 @@
   <si>
     <t>neo admission</t>
   </si>
+  <si>
+    <t>marup</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -513,13 +517,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -890,7 +894,7 @@
         <f>SUM(E26:E30)</f>
         <v>17380</v>
       </c>
-      <c r="F6" s="31"/>
+      <c r="F6" s="30"/>
     </row>
     <row r="7" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
@@ -939,7 +943,7 @@
       <c r="E13" s="19">
         <v>17500</v>
       </c>
-      <c r="F13" s="30"/>
+      <c r="F13" s="29"/>
     </row>
     <row r="14" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="9">
@@ -949,7 +953,7 @@
         <f>2000+3000+3000+2000</f>
         <v>10000</v>
       </c>
-      <c r="F14" s="30"/>
+      <c r="F14" s="29"/>
     </row>
     <row r="15" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="20">
@@ -958,7 +962,7 @@
       <c r="E15" s="19">
         <v>35000</v>
       </c>
-      <c r="F15" s="31"/>
+      <c r="F15" s="30"/>
     </row>
     <row r="16" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="9">
@@ -1462,7 +1466,7 @@
       </c>
     </row>
     <row r="5" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="29">
+      <c r="B5" s="31">
         <v>45274</v>
       </c>
       <c r="C5" s="28" t="s">
@@ -1476,7 +1480,7 @@
       </c>
     </row>
     <row r="6" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="29">
+      <c r="B6" s="31">
         <v>45283</v>
       </c>
       <c r="C6" s="28"/>
@@ -1488,7 +1492,7 @@
       </c>
     </row>
     <row r="7" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="29">
+      <c r="B7" s="31">
         <v>45301</v>
       </c>
       <c r="C7" s="28"/>
@@ -1500,7 +1504,7 @@
       </c>
     </row>
     <row r="8" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="29">
+      <c r="B8" s="31">
         <v>45327</v>
       </c>
       <c r="C8" s="28"/>
@@ -1512,7 +1516,7 @@
       </c>
     </row>
     <row r="9" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="29">
+      <c r="B9" s="31">
         <v>45380</v>
       </c>
       <c r="C9" s="28"/>
@@ -1523,47 +1527,89 @@
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="28"/>
+    <row r="10" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="31">
+        <v>45394</v>
+      </c>
       <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
+      <c r="D10" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="28">
+        <v>500</v>
+      </c>
     </row>
     <row r="11" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="28"/>
+      <c r="B11" s="31">
+        <v>45424</v>
+      </c>
       <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="28"/>
+      <c r="D11" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="28">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="31">
+        <v>45455</v>
+      </c>
       <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
+      <c r="D12" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="28">
+        <v>500</v>
+      </c>
     </row>
     <row r="13" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="28"/>
+      <c r="B13" s="31">
+        <v>45485</v>
+      </c>
       <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
+      <c r="D13" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="28">
+        <v>500</v>
+      </c>
     </row>
     <row r="14" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="28"/>
+      <c r="B14" s="31">
+        <v>45519</v>
+      </c>
       <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
+      <c r="D14" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="28">
+        <v>5000</v>
+      </c>
     </row>
     <row r="15" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="28"/>
+      <c r="B15" s="31">
+        <v>45544</v>
+      </c>
       <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
+      <c r="D15" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="28">
+        <v>5000</v>
+      </c>
     </row>
     <row r="16" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="28"/>
+      <c r="B16" s="31">
+        <v>45544</v>
+      </c>
       <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
+      <c r="D16" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="28">
+        <v>500</v>
+      </c>
     </row>
     <row r="17" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="28"/>
@@ -1588,5 +1634,6 @@
     <row r="27" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Financials.xlsx
+++ b/Financials.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="13" r:id="rId1"/>
-    <sheet name="BalanceSheet" sheetId="12" r:id="rId2"/>
-    <sheet name="Expenses" sheetId="14" r:id="rId3"/>
+    <sheet name="deposit" sheetId="15" r:id="rId2"/>
+    <sheet name="BalanceSheet" sheetId="12" r:id="rId3"/>
+    <sheet name="Expenses" sheetId="14" r:id="rId4"/>
   </sheets>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
   <si>
     <t>Balance Sheet</t>
   </si>
@@ -249,6 +250,21 @@
   </si>
   <si>
     <t>marup</t>
+  </si>
+  <si>
+    <t>A1 ranjit</t>
+  </si>
+  <si>
+    <t>A2 ranjita</t>
+  </si>
+  <si>
+    <t>robita</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>@2% per month</t>
   </si>
 </sst>
 </file>
@@ -353,7 +369,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -413,27 +429,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -514,16 +515,16 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -542,6 +543,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -894,7 +898,7 @@
         <f>SUM(E26:E30)</f>
         <v>17380</v>
       </c>
-      <c r="F6" s="30"/>
+      <c r="F6" s="29"/>
     </row>
     <row r="7" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
@@ -930,11 +934,9 @@
     </row>
     <row r="12" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>30</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="20">
@@ -943,7 +945,7 @@
       <c r="E13" s="19">
         <v>17500</v>
       </c>
-      <c r="F13" s="29"/>
+      <c r="F13" s="28"/>
     </row>
     <row r="14" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="9">
@@ -953,7 +955,7 @@
         <f>2000+3000+3000+2000</f>
         <v>10000</v>
       </c>
-      <c r="F14" s="29"/>
+      <c r="F14" s="28"/>
     </row>
     <row r="15" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="20">
@@ -962,7 +964,7 @@
       <c r="E15" s="19">
         <v>35000</v>
       </c>
-      <c r="F15" s="30"/>
+      <c r="F15" s="29"/>
     </row>
     <row r="16" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="9">
@@ -1034,7 +1036,7 @@
     </row>
     <row r="25" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="9" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E25" s="6"/>
     </row>
@@ -1079,6 +1081,198 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:F31"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.7109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="37" style="4" customWidth="1"/>
+    <col min="5" max="5" width="29" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3">
+        <v>45219</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="35"/>
+      <c r="E5" s="6">
+        <f>SUM(E13:E24)</f>
+        <v>10000</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="19">
+        <f>SUM(E26:E30)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="29"/>
+    </row>
+    <row r="7" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="5"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="22">
+        <f>SUM(E12:E30)</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="20">
+        <v>45647</v>
+      </c>
+      <c r="E13" s="19">
+        <v>10000</v>
+      </c>
+      <c r="F13" s="28"/>
+    </row>
+    <row r="14" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="9"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="28"/>
+    </row>
+    <row r="15" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="20"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="29"/>
+    </row>
+    <row r="16" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="9"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D17" s="20"/>
+      <c r="E17" s="19"/>
+    </row>
+    <row r="18" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="20"/>
+      <c r="E18" s="19"/>
+    </row>
+    <row r="19" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="9"/>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="9"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="9"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="9"/>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="26"/>
+      <c r="E23" s="27"/>
+    </row>
+    <row r="24" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="9"/>
+      <c r="E24" s="6"/>
+    </row>
+    <row r="25" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="9"/>
+      <c r="E25" s="6"/>
+    </row>
+    <row r="26" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="20"/>
+      <c r="E26" s="19"/>
+    </row>
+    <row r="27" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D27" s="9"/>
+      <c r="E27" s="6"/>
+    </row>
+    <row r="28" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="20"/>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="9"/>
+      <c r="E29" s="6"/>
+    </row>
+    <row r="30" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="20"/>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="4:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1434,15 +1628,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
-    <col min="2" max="3" width="12.7109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="4" customWidth="1"/>
     <col min="4" max="4" width="22.140625" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="4"/>
+    <col min="5" max="5" width="17" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1452,184 +1648,231 @@
       </c>
     </row>
     <row r="4" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="22" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="31">
+      <c r="B5" s="38">
         <v>45274</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="19">
         <v>480</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="31">
+      <c r="B6" s="38">
         <v>45283</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="19">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="31">
+      <c r="B7" s="38">
         <v>45301</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="19">
         <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="31">
+      <c r="B8" s="38">
         <v>45327</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="19">
         <v>10000</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="31">
+      <c r="B9" s="38">
         <v>45380</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28" t="s">
+      <c r="C9" s="19"/>
+      <c r="D9" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="19">
         <v>500</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="31">
+      <c r="B10" s="38">
         <v>45394</v>
       </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28" t="s">
+      <c r="C10" s="19"/>
+      <c r="D10" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="19">
         <v>500</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="31">
+      <c r="B11" s="38">
         <v>45424</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28" t="s">
+      <c r="C11" s="19"/>
+      <c r="D11" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="19">
         <v>500</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="31">
+      <c r="B12" s="38">
         <v>45455</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28" t="s">
+      <c r="C12" s="19"/>
+      <c r="D12" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="19">
         <v>500</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="31">
+      <c r="B13" s="38">
         <v>45485</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28" t="s">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="19">
         <v>500</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="31">
+      <c r="B14" s="38">
         <v>45519</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28" t="s">
+      <c r="C14" s="19"/>
+      <c r="D14" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="19">
         <v>5000</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="31">
+      <c r="B15" s="38">
         <v>45544</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="19">
         <v>5000</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="31">
+      <c r="B16" s="38">
         <v>45544</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="19"/>
+      <c r="D16" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="19">
         <v>500</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
+      <c r="B17" s="38">
+        <v>45611</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="19">
+        <v>6500</v>
+      </c>
     </row>
     <row r="18" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-    </row>
-    <row r="19" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B18" s="38">
+        <v>45640</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="19">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="38"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+    </row>
+    <row r="20" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="38"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+    </row>
+    <row r="21" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="38"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="38"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+    </row>
+    <row r="23" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="38"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+    </row>
+    <row r="24" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="38"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="38"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+    </row>
     <row r="26" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>

--- a/Financials.xlsx
+++ b/Financials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="13" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
   <si>
     <t>Balance Sheet</t>
   </si>
@@ -265,6 +265,39 @@
   </si>
   <si>
     <t>@2% per month</t>
+  </si>
+  <si>
+    <t>dividend:</t>
+  </si>
+  <si>
+    <t>ranjita balance:</t>
+  </si>
+  <si>
+    <t>pay to ranjit:</t>
+  </si>
+  <si>
+    <t>sales of rice:</t>
+  </si>
+  <si>
+    <t>8000+3500</t>
+  </si>
+  <si>
+    <t>ranjit deposit</t>
+  </si>
+  <si>
+    <t>ranjit deposit:</t>
+  </si>
+  <si>
+    <t>ranjit deposit total:</t>
+  </si>
+  <si>
+    <t>5000+2300</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Ranjit</t>
   </si>
 </sst>
 </file>
@@ -527,6 +560,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -543,9 +579,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -865,10 +898,10 @@
       <c r="B4" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="33"/>
+      <c r="D4" s="34"/>
       <c r="E4" s="21" t="s">
         <v>37</v>
       </c>
@@ -877,10 +910,10 @@
       <c r="B5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="35"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="6">
         <f>SUM(E13:E24)</f>
         <v>171000</v>
@@ -890,10 +923,10 @@
       <c r="B6" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="37"/>
+      <c r="D6" s="38"/>
       <c r="E6" s="19">
         <f>SUM(E26:E30)</f>
         <v>17380</v>
@@ -904,8 +937,8 @@
       <c r="B7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="6"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
@@ -1081,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:F31"/>
+  <dimension ref="B2:H31"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="4" customWidth="1"/>
@@ -1090,10 +1123,11 @@
     <col min="4" max="4" width="37" style="4" customWidth="1"/>
     <col min="5" max="5" width="29" style="4" customWidth="1"/>
     <col min="6" max="6" width="12.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="4"/>
+    <col min="7" max="7" width="17.5703125" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
         <v>39</v>
       </c>
@@ -1103,81 +1137,105 @@
         <v>45219</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="33"/>
+      <c r="D4" s="34"/>
       <c r="E4" s="21" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="35"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="6">
-        <f>SUM(E13:E24)</f>
+        <f>SUM(E13:E15)</f>
         <v>10000</v>
       </c>
       <c r="F5" s="31" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="18"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="19">
-        <f>SUM(E26:E30)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="29"/>
-    </row>
-    <row r="7" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="38"/>
+      <c r="E6" s="6">
+        <f>SUM(E18:E21)</f>
+        <v>7300</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
-    <row r="9" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="21" t="s">
         <v>34</v>
       </c>
       <c r="E9" s="22">
         <f>SUM(E12:E30)</f>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="15" x14ac:dyDescent="0.25">
+        <v>17300</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="15" x14ac:dyDescent="0.25">
       <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="4">
+        <v>14600</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="21" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="22" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="4">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="9" t="s">
         <v>61</v>
       </c>
       <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="20">
         <v>45647</v>
       </c>
@@ -1185,78 +1243,102 @@
         <v>10000</v>
       </c>
       <c r="F13" s="28"/>
-    </row>
-    <row r="14" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="4">
+        <v>-4200</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="9"/>
       <c r="E14" s="6"/>
       <c r="F14" s="28"/>
-    </row>
-    <row r="15" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="4">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="20"/>
       <c r="E15" s="19"/>
       <c r="F15" s="29"/>
-    </row>
-    <row r="16" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="9"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="20"/>
-      <c r="E17" s="19"/>
-    </row>
-    <row r="18" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="20"/>
-      <c r="E18" s="19"/>
-    </row>
-    <row r="19" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="4">
+        <v>-1900</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D17" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="20">
+        <v>45661</v>
+      </c>
+      <c r="E18" s="19">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="9"/>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="9"/>
       <c r="E20" s="6"/>
     </row>
-    <row r="21" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="9"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="9"/>
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="26"/>
-      <c r="E23" s="27"/>
-    </row>
-    <row r="24" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="9"/>
-      <c r="E24" s="6"/>
-    </row>
-    <row r="25" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="9"/>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="20"/>
       <c r="E26" s="19"/>
     </row>
-    <row r="27" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="9"/>
       <c r="E27" s="6"/>
     </row>
-    <row r="28" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="20"/>
       <c r="E28" s="19"/>
     </row>
-    <row r="29" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="9"/>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" spans="4:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="20"/>
       <c r="E30" s="19"/>
     </row>
-    <row r="31" spans="4:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:8" ht="15" x14ac:dyDescent="0.25">
       <c r="D31" s="10"/>
     </row>
   </sheetData>
@@ -1662,7 +1744,7 @@
       </c>
     </row>
     <row r="5" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="38">
+      <c r="B5" s="32">
         <v>45274</v>
       </c>
       <c r="C5" s="19" t="s">
@@ -1676,7 +1758,7 @@
       </c>
     </row>
     <row r="6" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="38">
+      <c r="B6" s="32">
         <v>45283</v>
       </c>
       <c r="C6" s="19"/>
@@ -1688,7 +1770,7 @@
       </c>
     </row>
     <row r="7" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="38">
+      <c r="B7" s="32">
         <v>45301</v>
       </c>
       <c r="C7" s="19"/>
@@ -1700,7 +1782,7 @@
       </c>
     </row>
     <row r="8" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="38">
+      <c r="B8" s="32">
         <v>45327</v>
       </c>
       <c r="C8" s="19"/>
@@ -1712,7 +1794,7 @@
       </c>
     </row>
     <row r="9" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="38">
+      <c r="B9" s="32">
         <v>45380</v>
       </c>
       <c r="C9" s="19"/>
@@ -1724,7 +1806,7 @@
       </c>
     </row>
     <row r="10" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="38">
+      <c r="B10" s="32">
         <v>45394</v>
       </c>
       <c r="C10" s="19"/>
@@ -1736,7 +1818,7 @@
       </c>
     </row>
     <row r="11" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="38">
+      <c r="B11" s="32">
         <v>45424</v>
       </c>
       <c r="C11" s="19"/>
@@ -1748,7 +1830,7 @@
       </c>
     </row>
     <row r="12" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="38">
+      <c r="B12" s="32">
         <v>45455</v>
       </c>
       <c r="C12" s="19"/>
@@ -1760,7 +1842,7 @@
       </c>
     </row>
     <row r="13" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="38">
+      <c r="B13" s="32">
         <v>45485</v>
       </c>
       <c r="C13" s="19"/>
@@ -1772,7 +1854,7 @@
       </c>
     </row>
     <row r="14" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="38">
+      <c r="B14" s="32">
         <v>45519</v>
       </c>
       <c r="C14" s="19"/>
@@ -1784,7 +1866,7 @@
       </c>
     </row>
     <row r="15" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="38">
+      <c r="B15" s="32">
         <v>45544</v>
       </c>
       <c r="C15" s="19"/>
@@ -1796,7 +1878,7 @@
       </c>
     </row>
     <row r="16" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="38">
+      <c r="B16" s="32">
         <v>45544</v>
       </c>
       <c r="C16" s="19"/>
@@ -1808,7 +1890,7 @@
       </c>
     </row>
     <row r="17" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="38">
+      <c r="B17" s="32">
         <v>45611</v>
       </c>
       <c r="C17" s="19"/>
@@ -1820,7 +1902,7 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="38">
+      <c r="B18" s="32">
         <v>45640</v>
       </c>
       <c r="C18" s="19"/>
@@ -1832,43 +1914,43 @@
       </c>
     </row>
     <row r="19" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="38"/>
+      <c r="B19" s="32"/>
       <c r="C19" s="19"/>
       <c r="D19" s="19"/>
       <c r="E19" s="19"/>
     </row>
     <row r="20" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="38"/>
+      <c r="B20" s="32"/>
       <c r="C20" s="19"/>
       <c r="D20" s="19"/>
       <c r="E20" s="19"/>
     </row>
     <row r="21" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="38"/>
+      <c r="B21" s="32"/>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="38"/>
+      <c r="B22" s="32"/>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
     </row>
     <row r="23" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="38"/>
+      <c r="B23" s="32"/>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
     </row>
     <row r="24" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="38"/>
+      <c r="B24" s="32"/>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
     </row>
     <row r="25" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="38"/>
+      <c r="B25" s="32"/>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>

--- a/Financials.xlsx
+++ b/Financials.xlsx
@@ -864,7 +864,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1175,7 +1175,7 @@
       <c r="D6" s="38"/>
       <c r="E6" s="6">
         <f>SUM(E18:E21)</f>
-        <v>7300</v>
+        <v>11300</v>
       </c>
       <c r="F6" s="31" t="s">
         <v>62</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E9" s="22">
         <f>SUM(E12:E30)</f>
-        <v>17300</v>
+        <v>21300</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15" x14ac:dyDescent="0.25">
@@ -1300,8 +1300,12 @@
       </c>
     </row>
     <row r="19" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="9"/>
-      <c r="E19" s="6"/>
+      <c r="D19" s="9">
+        <v>45707</v>
+      </c>
+      <c r="E19" s="6">
+        <v>4000</v>
+      </c>
     </row>
     <row r="20" spans="4:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="9"/>

--- a/Financials.xlsx
+++ b/Financials.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="13" r:id="rId1"/>
     <sheet name="deposit" sheetId="15" r:id="rId2"/>
     <sheet name="BalanceSheet" sheetId="12" r:id="rId3"/>
     <sheet name="Expenses" sheetId="14" r:id="rId4"/>
+    <sheet name="anand" sheetId="16" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="104">
   <si>
     <t>Balance Sheet</t>
   </si>
@@ -299,18 +300,109 @@
   <si>
     <t>Ranjit</t>
   </si>
+  <si>
+    <t>Anand 1st installment of loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - rice Rs 21000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Tungfam Rs 3250</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Aboong Rs 11750</t>
+  </si>
+  <si>
+    <t>Anand 2nd Installment of Loan</t>
+  </si>
+  <si>
+    <t>credit card</t>
+  </si>
+  <si>
+    <t>hdfc bank - suresh 5000 for rice like 2025</t>
+  </si>
+  <si>
+    <t>credit  card - Rs 16000 Rs 11000 for tunfam</t>
+  </si>
+  <si>
+    <t>from bechau</t>
+  </si>
+  <si>
+    <t>to bechau</t>
+  </si>
+  <si>
+    <t>to and from gpay</t>
+  </si>
+  <si>
+    <t>from bechau Cash</t>
+  </si>
+  <si>
+    <t>Emoinu - Bechau</t>
+  </si>
+  <si>
+    <t>grocery/vegetables from tungfam</t>
+  </si>
+  <si>
+    <t>naobi marup Rs 500 for bechau</t>
+  </si>
+  <si>
+    <t>gas cylinder for ema Rs 1200</t>
+  </si>
+  <si>
+    <t>Emoinu = Ema Rs 1500</t>
+  </si>
+  <si>
+    <t>grocery</t>
+  </si>
+  <si>
+    <t>bomcha marup</t>
+  </si>
+  <si>
+    <t>Anand final Installment of Loan from bechau</t>
+  </si>
+  <si>
+    <t>bomcha marup 11500-3000 = 8500</t>
+  </si>
+  <si>
+    <t>angom marup 11000-2500 = 8500</t>
+  </si>
+  <si>
+    <t>tungfam balance with aboong 31100 - 3000 = 28100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1st and 2nd installment - 11750 + 14000 = 25750 </t>
+  </si>
+  <si>
+    <t>expenditure from aboong's fund = 25750+8500+8500=42750</t>
+  </si>
+  <si>
+    <t>payable to aboong by Tungfam 41000-28100 = 14650</t>
+  </si>
+  <si>
+    <t>rice</t>
+  </si>
+  <si>
+    <t>3rd installment</t>
+  </si>
+  <si>
+    <t>aboongm</t>
+  </si>
+  <si>
+    <t>tungfam online transaction</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="168" formatCode="[$₹-4009]#,##0.00;[Red]\-[$₹-4009]#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,8 +461,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -401,8 +499,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor rgb="FF003300"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -462,12 +572,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -580,6 +705,17 @@
     </xf>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -864,7 +1000,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1965,4 +2101,511 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:H45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="42"/>
+    <col min="2" max="2" width="12.7109375" style="42" customWidth="1"/>
+    <col min="3" max="3" width="41.42578125" style="42" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="42" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="42" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="42" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="42"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="39">
+        <v>45985</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="41">
+        <v>36000</v>
+      </c>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="39"/>
+      <c r="C3" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="39"/>
+      <c r="C4" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="39"/>
+      <c r="C5" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="39">
+        <v>46021</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="41">
+        <v>14000</v>
+      </c>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="39">
+        <v>46033</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="41">
+        <v>10000</v>
+      </c>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="39">
+        <v>46020</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="41">
+        <v>8000</v>
+      </c>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="39">
+        <v>46385</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="39">
+        <v>46034</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="41">
+        <v>11000</v>
+      </c>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="39"/>
+      <c r="C18" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="39">
+        <v>46021</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="41">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="39">
+        <v>46021</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="41">
+        <v>7500</v>
+      </c>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="39">
+        <v>46021</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41">
+        <v>1500</v>
+      </c>
+      <c r="F21" s="41"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="39">
+        <v>46021</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="39">
+        <v>46023</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="41">
+        <v>2000</v>
+      </c>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="39">
+        <v>46026</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F24" s="41"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="39">
+        <v>46033</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="41">
+        <v>4000</v>
+      </c>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="39">
+        <v>46033</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="39">
+        <v>46034</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="41">
+        <v>1200</v>
+      </c>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="39">
+        <v>46034</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41">
+        <v>500</v>
+      </c>
+      <c r="F28" s="41"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="39">
+        <v>46037</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="39">
+        <v>46037</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="41">
+        <v>3000</v>
+      </c>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="39">
+        <v>46043</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" s="41">
+        <v>4900</v>
+      </c>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="39">
+        <v>46046</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="41">
+        <v>2500</v>
+      </c>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="39">
+        <v>46049</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" s="41">
+        <v>5000</v>
+      </c>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="39"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="39"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="39"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="41">
+        <f>SUM(D19:D33)</f>
+        <v>31100</v>
+      </c>
+      <c r="E36" s="41">
+        <f>SUM(E19:E33)</f>
+        <v>3000</v>
+      </c>
+      <c r="F36" s="41"/>
+    </row>
+    <row r="37" spans="2:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="B37" s="39"/>
+      <c r="C37" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="39"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="39"/>
+      <c r="C39" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="39"/>
+      <c r="C40" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="42">
+        <v>-12500</v>
+      </c>
+      <c r="H40" s="42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="39"/>
+      <c r="C41" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="42">
+        <v>21000</v>
+      </c>
+      <c r="H41" s="42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="39"/>
+      <c r="C42" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="42">
+        <v>10000</v>
+      </c>
+      <c r="H42" s="42" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="39"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="42">
+        <v>14650</v>
+      </c>
+      <c r="H43" s="42" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="B44" s="39">
+        <v>46049</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="42">
+        <v>28100</v>
+      </c>
+      <c r="H44" s="42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="39"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="42">
+        <f>SUM(G40:G44)</f>
+        <v>61250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>